--- a/03_Coding_Sheets/70_94_109.xlsx
+++ b/03_Coding_Sheets/70_94_109.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Organizations were ranked from 1 (small) to 3 (large)</t>
+          <t>Organizational size was determined by the total number of technical professionals, both managers and non-managers, located at the site. Organizations were ranked from 1 (small) to 3 (large)</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>A 9-item short form was used (Angle &amp; Perry, 1981).</t>
+          <t>The Organizational Commitment Questionnaire (OCQ) (Porter et. al., 1974) is widely used and generally the preferred measure of organizational commitment (Ferris &amp; Aranya, 1983). A 9-item short form was used (Angle &amp; Perry, 1981).</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Both sets of commitment items were measured using a 7-point Likert-type scale from 1=strongly disagree to 7=strongly agree.</t>
+          <t>This variable was measured using a format similar to the OCQ following Lachman &amp; Aranya (1986). Both sets of commitment items were measured using a 7-point Likert-type scale from 1=strongly disagree to 7=strongly agree.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Subjects were asked to indicate what percentage of their work falls into each of four categories.</t>
+          <t>All of the above researchers used a weighted sum of the percentages as a measure of task complexity. Subjects were asked to indicate what percentage of their work falls into each of four categories.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>The decision was made to delete the intraproject coordination item.</t>
+          <t>For the Extraproject Coordination scale, with intraproject coordination deleted, alpha was .63. The decision was made to delete the intraproject coordination item.</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Organizations were ranked from 1 (small) to 3 (large)</t>
+          <t>Organizational size was determined by the total number of technical professionals, both managers and non-managers, located at the site. Organizations were ranked from 1 (small) to 3 (large)</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>A 9-item short form was used (Angle &amp; Perry, 1981).</t>
+          <t>The Organizational Commitment Questionnaire (OCQ) (Porter et. al., 1974) is widely used and generally the preferred measure of organizational commitment (Ferris &amp; Aranya, 1983). A 9-item short form was used (Angle &amp; Perry, 1981).</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Both sets of commitment items were measured using a 7-point Likert-type scale from 1=strongly disagree to 7=strongly agree.</t>
+          <t>This variable was measured using a format similar to the OCQ following Lachman &amp; Aranya (1986). Both sets of commitment items were measured using a 7-point Likert-type scale from 1=strongly disagree to 7=strongly agree.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Subjects were asked to indicate what percentage of their work falls into each of four categories.</t>
+          <t>All of the above researchers used a weighted sum of the percentages as a measure of task complexity. Subjects were asked to indicate what percentage of their work falls into each of four categories.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>The decision was made to delete the intraproject coordination item.</t>
+          <t>For the Extraproject Coordination scale, with intraproject coordination deleted, alpha was .63. The decision was made to delete the intraproject coordination item.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH30" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH31" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Organizations were ranked from 1 (small) to 3 (large)</t>
+          <t>Organizational size was determined by the total number of technical professionals, both managers and non-managers, located at the site. Organizations were ranked from 1 (small) to 3 (large)</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH32" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH33" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>A 9-item short form was used (Angle &amp; Perry, 1981).</t>
+          <t>The Organizational Commitment Questionnaire (OCQ) (Porter et. al., 1974) is widely used and generally the preferred measure of organizational commitment (Ferris &amp; Aranya, 1983). A 9-item short form was used (Angle &amp; Perry, 1981).</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH34" t="n">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>Both sets of commitment items were measured using a 7-point Likert-type scale from 1=strongly disagree to 7=strongly agree.</t>
+          <t>This variable was measured using a format similar to the OCQ following Lachman &amp; Aranya (1986). Both sets of commitment items were measured using a 7-point Likert-type scale from 1=strongly disagree to 7=strongly agree.</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH35" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH36" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>Subjects were asked to indicate what percentage of their work falls into each of four categories.</t>
+          <t>All of the above researchers used a weighted sum of the percentages as a measure of task complexity. Subjects were asked to indicate what percentage of their work falls into each of four categories.</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH37" t="n">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH38" t="n">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>The decision was made to delete the intraproject coordination item.</t>
+          <t>For the Extraproject Coordination scale, with intraproject coordination deleted, alpha was .63. The decision was made to delete the intraproject coordination item.</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH39" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH40" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH41" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
+          <t>Intraunit communication frequency is one of the two components of boundary spanning activity. Subjects were asked about communication frequency within the last month with every other technical professional in the unit, using a 6-point Likert-type scale (0=never, 1=about once a month, 2=less than once a week, 3=about once a week, 4=more than once a week, 5=almost every day).</t>
         </is>
       </c>
       <c r="AH42" t="n">
